--- a/output/26.9_SAP_重複商品集計.xlsx
+++ b/output/26.9_SAP_重複商品集計.xlsx
@@ -5,16 +5,16 @@
   <sheets>
     <sheet name="XTab DS_1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Filter DS_1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="重複_CX催事" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="重複_DBS倉庫" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="重複_その他" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="重複商品_合算" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="倉庫別_CX催事" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="倉庫別_DBS倉庫" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="倉庫別_その他" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="商品別_合算" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'重複_CX催事'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'重複_DBS倉庫'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'重複_その他'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'重複商品_合算'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'倉庫別_CX催事'!$A$1:$H$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'倉庫別_DBS倉庫'!$A$1:$H$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'倉庫別_その他'!$A$1:$H$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'商品別_合算'!$A$1:$M$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -62,7 +62,7 @@
       <color rgb="00595959"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -76,7 +76,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -113,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -135,14 +145,28 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3943,7 +3967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="2" min="1" max="1"/>
@@ -3951,8 +3975,9 @@
     <col width="52" customWidth="1" style="2" min="3" max="3"/>
     <col width="10" customWidth="1" style="2" min="4" max="4"/>
     <col width="12" customWidth="1" style="2" min="5" max="5"/>
-    <col width="14" customWidth="1" style="2" min="6" max="6"/>
-    <col width="16" customWidth="1" style="2" min="7" max="7"/>
+    <col width="8" customWidth="1" style="2" min="6" max="6"/>
+    <col width="14" customWidth="1" style="2" min="7" max="7"/>
+    <col width="16" customWidth="1" style="2" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3983,10 +4008,15 @@
       </c>
       <c r="F1" s="8" t="inlineStr">
         <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
           <t>在庫数量</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>在庫金額</t>
         </is>
@@ -4019,10 +4049,14 @@
         </is>
       </c>
       <c r="F2" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B2)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G2" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B2,'XTab DS_1'!$D$2:$D$95,$D2)</f>
         <v/>
       </c>
-      <c r="G2" s="11">
+      <c r="H2" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B2,'XTab DS_1'!$D$2:$D$95,$D2)</f>
         <v/>
       </c>
@@ -4054,10 +4088,14 @@
         </is>
       </c>
       <c r="F3" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B3)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G3" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B3,'XTab DS_1'!$D$2:$D$95,$D3)</f>
         <v/>
       </c>
-      <c r="G3" s="11">
+      <c r="H3" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B3,'XTab DS_1'!$D$2:$D$95,$D3)</f>
         <v/>
       </c>
@@ -4089,10 +4127,14 @@
         </is>
       </c>
       <c r="F4" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B4)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G4" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B4,'XTab DS_1'!$D$2:$D$95,$D4)</f>
         <v/>
       </c>
-      <c r="G4" s="11">
+      <c r="H4" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B4,'XTab DS_1'!$D$2:$D$95,$D4)</f>
         <v/>
       </c>
@@ -4124,10 +4166,14 @@
         </is>
       </c>
       <c r="F5" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B5)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G5" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B5,'XTab DS_1'!$D$2:$D$95,$D5)</f>
         <v/>
       </c>
-      <c r="G5" s="11">
+      <c r="H5" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B5,'XTab DS_1'!$D$2:$D$95,$D5)</f>
         <v/>
       </c>
@@ -4159,10 +4205,14 @@
         </is>
       </c>
       <c r="F6" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B6)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G6" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B6,'XTab DS_1'!$D$2:$D$95,$D6)</f>
         <v/>
       </c>
-      <c r="G6" s="11">
+      <c r="H6" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B6,'XTab DS_1'!$D$2:$D$95,$D6)</f>
         <v/>
       </c>
@@ -4194,10 +4244,14 @@
         </is>
       </c>
       <c r="F7" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B7)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G7" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B7,'XTab DS_1'!$D$2:$D$95,$D7)</f>
         <v/>
       </c>
-      <c r="G7" s="11">
+      <c r="H7" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B7,'XTab DS_1'!$D$2:$D$95,$D7)</f>
         <v/>
       </c>
@@ -4229,10 +4283,14 @@
         </is>
       </c>
       <c r="F8" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B8)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G8" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B8,'XTab DS_1'!$D$2:$D$95,$D8)</f>
         <v/>
       </c>
-      <c r="G8" s="11">
+      <c r="H8" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B8,'XTab DS_1'!$D$2:$D$95,$D8)</f>
         <v/>
       </c>
@@ -4264,10 +4322,14 @@
         </is>
       </c>
       <c r="F9" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B9)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G9" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B9,'XTab DS_1'!$D$2:$D$95,$D9)</f>
         <v/>
       </c>
-      <c r="G9" s="11">
+      <c r="H9" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B9,'XTab DS_1'!$D$2:$D$95,$D9)</f>
         <v/>
       </c>
@@ -4299,10 +4361,14 @@
         </is>
       </c>
       <c r="F10" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B10)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G10" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B10,'XTab DS_1'!$D$2:$D$95,$D10)</f>
         <v/>
       </c>
-      <c r="G10" s="11">
+      <c r="H10" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B10,'XTab DS_1'!$D$2:$D$95,$D10)</f>
         <v/>
       </c>
@@ -4334,10 +4400,14 @@
         </is>
       </c>
       <c r="F11" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B11)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G11" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B11,'XTab DS_1'!$D$2:$D$95,$D11)</f>
         <v/>
       </c>
-      <c r="G11" s="11">
+      <c r="H11" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B11,'XTab DS_1'!$D$2:$D$95,$D11)</f>
         <v/>
       </c>
@@ -4369,10 +4439,14 @@
         </is>
       </c>
       <c r="F12" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B12)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G12" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B12,'XTab DS_1'!$D$2:$D$95,$D12)</f>
         <v/>
       </c>
-      <c r="G12" s="11">
+      <c r="H12" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B12,'XTab DS_1'!$D$2:$D$95,$D12)</f>
         <v/>
       </c>
@@ -4404,10 +4478,14 @@
         </is>
       </c>
       <c r="F13" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B13)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G13" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B13,'XTab DS_1'!$D$2:$D$95,$D13)</f>
         <v/>
       </c>
-      <c r="G13" s="11">
+      <c r="H13" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B13,'XTab DS_1'!$D$2:$D$95,$D13)</f>
         <v/>
       </c>
@@ -4439,10 +4517,14 @@
         </is>
       </c>
       <c r="F14" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B14)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G14" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B14,'XTab DS_1'!$D$2:$D$95,$D14)</f>
         <v/>
       </c>
-      <c r="G14" s="11">
+      <c r="H14" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B14,'XTab DS_1'!$D$2:$D$95,$D14)</f>
         <v/>
       </c>
@@ -4474,10 +4556,14 @@
         </is>
       </c>
       <c r="F15" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B15)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G15" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B15,'XTab DS_1'!$D$2:$D$95,$D15)</f>
         <v/>
       </c>
-      <c r="G15" s="11">
+      <c r="H15" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B15,'XTab DS_1'!$D$2:$D$95,$D15)</f>
         <v/>
       </c>
@@ -4509,10 +4595,14 @@
         </is>
       </c>
       <c r="F16" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B16)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G16" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B16,'XTab DS_1'!$D$2:$D$95,$D16)</f>
         <v/>
       </c>
-      <c r="G16" s="11">
+      <c r="H16" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B16,'XTab DS_1'!$D$2:$D$95,$D16)</f>
         <v/>
       </c>
@@ -4544,10 +4634,14 @@
         </is>
       </c>
       <c r="F17" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B17)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G17" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B17,'XTab DS_1'!$D$2:$D$95,$D17)</f>
         <v/>
       </c>
-      <c r="G17" s="11">
+      <c r="H17" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B17,'XTab DS_1'!$D$2:$D$95,$D17)</f>
         <v/>
       </c>
@@ -4579,10 +4673,14 @@
         </is>
       </c>
       <c r="F18" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B18)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G18" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B18,'XTab DS_1'!$D$2:$D$95,$D18)</f>
         <v/>
       </c>
-      <c r="G18" s="11">
+      <c r="H18" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B18,'XTab DS_1'!$D$2:$D$95,$D18)</f>
         <v/>
       </c>
@@ -4614,10 +4712,14 @@
         </is>
       </c>
       <c r="F19" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B19)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G19" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B19,'XTab DS_1'!$D$2:$D$95,$D19)</f>
         <v/>
       </c>
-      <c r="G19" s="11">
+      <c r="H19" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B19,'XTab DS_1'!$D$2:$D$95,$D19)</f>
         <v/>
       </c>
@@ -4649,10 +4751,14 @@
         </is>
       </c>
       <c r="F20" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B20)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G20" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B20,'XTab DS_1'!$D$2:$D$95,$D20)</f>
         <v/>
       </c>
-      <c r="G20" s="11">
+      <c r="H20" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B20,'XTab DS_1'!$D$2:$D$95,$D20)</f>
         <v/>
       </c>
@@ -4684,10 +4790,14 @@
         </is>
       </c>
       <c r="F21" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B21)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G21" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B21,'XTab DS_1'!$D$2:$D$95,$D21)</f>
         <v/>
       </c>
-      <c r="G21" s="11">
+      <c r="H21" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B21,'XTab DS_1'!$D$2:$D$95,$D21)</f>
         <v/>
       </c>
@@ -4719,10 +4829,14 @@
         </is>
       </c>
       <c r="F22" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B22)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G22" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B22,'XTab DS_1'!$D$2:$D$95,$D22)</f>
         <v/>
       </c>
-      <c r="G22" s="11">
+      <c r="H22" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B22,'XTab DS_1'!$D$2:$D$95,$D22)</f>
         <v/>
       </c>
@@ -4754,10 +4868,14 @@
         </is>
       </c>
       <c r="F23" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B23)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G23" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B23,'XTab DS_1'!$D$2:$D$95,$D23)</f>
         <v/>
       </c>
-      <c r="G23" s="11">
+      <c r="H23" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B23,'XTab DS_1'!$D$2:$D$95,$D23)</f>
         <v/>
       </c>
@@ -4789,10 +4907,14 @@
         </is>
       </c>
       <c r="F24" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B24)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G24" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B24,'XTab DS_1'!$D$2:$D$95,$D24)</f>
         <v/>
       </c>
-      <c r="G24" s="11">
+      <c r="H24" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B24,'XTab DS_1'!$D$2:$D$95,$D24)</f>
         <v/>
       </c>
@@ -4824,10 +4946,14 @@
         </is>
       </c>
       <c r="F25" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B25)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G25" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B25,'XTab DS_1'!$D$2:$D$95,$D25)</f>
         <v/>
       </c>
-      <c r="G25" s="11">
+      <c r="H25" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B25,'XTab DS_1'!$D$2:$D$95,$D25)</f>
         <v/>
       </c>
@@ -4859,10 +4985,14 @@
         </is>
       </c>
       <c r="F26" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B26)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G26" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B26,'XTab DS_1'!$D$2:$D$95,$D26)</f>
         <v/>
       </c>
-      <c r="G26" s="11">
+      <c r="H26" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B26,'XTab DS_1'!$D$2:$D$95,$D26)</f>
         <v/>
       </c>
@@ -4894,10 +5024,14 @@
         </is>
       </c>
       <c r="F27" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B27)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G27" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B27,'XTab DS_1'!$D$2:$D$95,$D27)</f>
         <v/>
       </c>
-      <c r="G27" s="11">
+      <c r="H27" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B27,'XTab DS_1'!$D$2:$D$95,$D27)</f>
         <v/>
       </c>
@@ -4929,10 +5063,14 @@
         </is>
       </c>
       <c r="F28" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B28)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G28" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B28,'XTab DS_1'!$D$2:$D$95,$D28)</f>
         <v/>
       </c>
-      <c r="G28" s="11">
+      <c r="H28" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B28,'XTab DS_1'!$D$2:$D$95,$D28)</f>
         <v/>
       </c>
@@ -4964,10 +5102,14 @@
         </is>
       </c>
       <c r="F29" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B29)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G29" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B29,'XTab DS_1'!$D$2:$D$95,$D29)</f>
         <v/>
       </c>
-      <c r="G29" s="11">
+      <c r="H29" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B29,'XTab DS_1'!$D$2:$D$95,$D29)</f>
         <v/>
       </c>
@@ -4999,10 +5141,14 @@
         </is>
       </c>
       <c r="F30" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B30)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G30" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B30,'XTab DS_1'!$D$2:$D$95,$D30)</f>
         <v/>
       </c>
-      <c r="G30" s="11">
+      <c r="H30" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B30,'XTab DS_1'!$D$2:$D$95,$D30)</f>
         <v/>
       </c>
@@ -5034,10 +5180,14 @@
         </is>
       </c>
       <c r="F31" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B31)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G31" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B31,'XTab DS_1'!$D$2:$D$95,$D31)</f>
         <v/>
       </c>
-      <c r="G31" s="11">
+      <c r="H31" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B31,'XTab DS_1'!$D$2:$D$95,$D31)</f>
         <v/>
       </c>
@@ -5069,10 +5219,14 @@
         </is>
       </c>
       <c r="F32" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B32)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G32" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B32,'XTab DS_1'!$D$2:$D$95,$D32)</f>
         <v/>
       </c>
-      <c r="G32" s="11">
+      <c r="H32" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B32,'XTab DS_1'!$D$2:$D$95,$D32)</f>
         <v/>
       </c>
@@ -5104,10 +5258,14 @@
         </is>
       </c>
       <c r="F33" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B33)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G33" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B33,'XTab DS_1'!$D$2:$D$95,$D33)</f>
         <v/>
       </c>
-      <c r="G33" s="11">
+      <c r="H33" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B33,'XTab DS_1'!$D$2:$D$95,$D33)</f>
         <v/>
       </c>
@@ -5139,10 +5297,14 @@
         </is>
       </c>
       <c r="F34" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B34)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G34" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B34,'XTab DS_1'!$D$2:$D$95,$D34)</f>
         <v/>
       </c>
-      <c r="G34" s="11">
+      <c r="H34" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B34,'XTab DS_1'!$D$2:$D$95,$D34)</f>
         <v/>
       </c>
@@ -5174,10 +5336,14 @@
         </is>
       </c>
       <c r="F35" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B35)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G35" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B35,'XTab DS_1'!$D$2:$D$95,$D35)</f>
         <v/>
       </c>
-      <c r="G35" s="11">
+      <c r="H35" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B35,'XTab DS_1'!$D$2:$D$95,$D35)</f>
         <v/>
       </c>
@@ -5209,10 +5375,14 @@
         </is>
       </c>
       <c r="F36" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B36)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G36" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B36,'XTab DS_1'!$D$2:$D$95,$D36)</f>
         <v/>
       </c>
-      <c r="G36" s="11">
+      <c r="H36" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B36,'XTab DS_1'!$D$2:$D$95,$D36)</f>
         <v/>
       </c>
@@ -5244,10 +5414,14 @@
         </is>
       </c>
       <c r="F37" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B37)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G37" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B37,'XTab DS_1'!$D$2:$D$95,$D37)</f>
         <v/>
       </c>
-      <c r="G37" s="11">
+      <c r="H37" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B37,'XTab DS_1'!$D$2:$D$95,$D37)</f>
         <v/>
       </c>
@@ -5279,10 +5453,14 @@
         </is>
       </c>
       <c r="F38" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B38)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G38" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B38,'XTab DS_1'!$D$2:$D$95,$D38)</f>
         <v/>
       </c>
-      <c r="G38" s="11">
+      <c r="H38" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B38,'XTab DS_1'!$D$2:$D$95,$D38)</f>
         <v/>
       </c>
@@ -5314,10 +5492,14 @@
         </is>
       </c>
       <c r="F39" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B39)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G39" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B39,'XTab DS_1'!$D$2:$D$95,$D39)</f>
         <v/>
       </c>
-      <c r="G39" s="11">
+      <c r="H39" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B39,'XTab DS_1'!$D$2:$D$95,$D39)</f>
         <v/>
       </c>
@@ -5349,10 +5531,14 @@
         </is>
       </c>
       <c r="F40" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B40)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G40" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B40,'XTab DS_1'!$D$2:$D$95,$D40)</f>
         <v/>
       </c>
-      <c r="G40" s="11">
+      <c r="H40" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B40,'XTab DS_1'!$D$2:$D$95,$D40)</f>
         <v/>
       </c>
@@ -5384,10 +5570,14 @@
         </is>
       </c>
       <c r="F41" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B41)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G41" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B41,'XTab DS_1'!$D$2:$D$95,$D41)</f>
         <v/>
       </c>
-      <c r="G41" s="11">
+      <c r="H41" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B41,'XTab DS_1'!$D$2:$D$95,$D41)</f>
         <v/>
       </c>
@@ -5419,10 +5609,14 @@
         </is>
       </c>
       <c r="F42" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B42)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G42" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B42,'XTab DS_1'!$D$2:$D$95,$D42)</f>
         <v/>
       </c>
-      <c r="G42" s="11">
+      <c r="H42" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B42,'XTab DS_1'!$D$2:$D$95,$D42)</f>
         <v/>
       </c>
@@ -5454,10 +5648,14 @@
         </is>
       </c>
       <c r="F43" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B43)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G43" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B43,'XTab DS_1'!$D$2:$D$95,$D43)</f>
         <v/>
       </c>
-      <c r="G43" s="11">
+      <c r="H43" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B43,'XTab DS_1'!$D$2:$D$95,$D43)</f>
         <v/>
       </c>
@@ -5489,10 +5687,14 @@
         </is>
       </c>
       <c r="F44" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B44)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G44" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B44,'XTab DS_1'!$D$2:$D$95,$D44)</f>
         <v/>
       </c>
-      <c r="G44" s="11">
+      <c r="H44" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B44,'XTab DS_1'!$D$2:$D$95,$D44)</f>
         <v/>
       </c>
@@ -5524,35 +5726,197 @@
         </is>
       </c>
       <c r="F45" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B45)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G45" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B45,'XTab DS_1'!$D$2:$D$95,$D45)</f>
         <v/>
       </c>
-      <c r="G45" s="11">
+      <c r="H45" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B45,'XTab DS_1'!$D$2:$D$95,$D45)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="12" t="n"/>
-      <c r="B46" s="12" t="n"/>
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>QCX2509JKS2FN-8</t>
+        </is>
+      </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
+          <t>呪術廻戦展 懐玉玉折 渋谷事変 経費（課税8％）</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="inlineStr">
+        <is>
+          <t>CX01</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>CX催事</t>
+        </is>
+      </c>
+      <c r="F46" s="14">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B46)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G46" s="15">
+        <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B46,'XTab DS_1'!$D$2:$D$95,$D46)</f>
+        <v/>
+      </c>
+      <c r="H46" s="16">
+        <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B46,'XTab DS_1'!$D$2:$D$95,$D46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>QCX2509JKS2FN-NT</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>呪術廻戦展 懐玉玉折 渋谷事変 経費（非課税）</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="inlineStr">
+        <is>
+          <t>CX01</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>CX催事</t>
+        </is>
+      </c>
+      <c r="F47" s="14">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B47)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G47" s="15">
+        <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B47,'XTab DS_1'!$D$2:$D$95,$D47)</f>
+        <v/>
+      </c>
+      <c r="H47" s="16">
+        <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B47,'XTab DS_1'!$D$2:$D$95,$D47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>QCX2509JKS2FN-RY</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>呪術廻戦展 懐玉玉折 渋谷事変 経費（RY）</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>CX01</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>CX催事</t>
+        </is>
+      </c>
+      <c r="F48" s="14">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B48)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G48" s="15">
+        <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B48,'XTab DS_1'!$D$2:$D$95,$D48)</f>
+        <v/>
+      </c>
+      <c r="H48" s="16">
+        <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B48,'XTab DS_1'!$D$2:$D$95,$D48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="17" t="n"/>
+      <c r="B49" s="17" t="n"/>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="D46" s="12" t="n"/>
-      <c r="E46" s="12" t="n"/>
-      <c r="F46" s="14">
-        <f>SUM(F2:F45)</f>
-        <v/>
-      </c>
-      <c r="G46" s="15">
-        <f>SUM(G2:G45)</f>
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n"/>
+      <c r="F49" s="17" t="n"/>
+      <c r="G49" s="19">
+        <f>SUM(G2:G48)</f>
+        <v/>
+      </c>
+      <c r="H49" s="20">
+        <f>SUM(H2:H48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="21" t="n"/>
+      <c r="B50" s="21" t="n"/>
+      <c r="C50" s="22" t="inlineStr">
+        <is>
+          <t>うち 重複</t>
+        </is>
+      </c>
+      <c r="D50" s="21" t="n"/>
+      <c r="E50" s="21" t="n"/>
+      <c r="F50" s="21" t="n"/>
+      <c r="G50" s="23">
+        <f>SUMIFS(G2:G48,F2:F48,"重複")</f>
+        <v/>
+      </c>
+      <c r="H50" s="24">
+        <f>SUMIFS(H2:H48,F2:F48,"重複")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="21" t="n"/>
+      <c r="B51" s="21" t="n"/>
+      <c r="C51" s="22" t="inlineStr">
+        <is>
+          <t>うち 単独</t>
+        </is>
+      </c>
+      <c r="D51" s="21" t="n"/>
+      <c r="E51" s="21" t="n"/>
+      <c r="F51" s="21" t="n"/>
+      <c r="G51" s="23">
+        <f>SUMIFS(G2:G48,F2:F48,"単独")</f>
+        <v/>
+      </c>
+      <c r="H51" s="24">
+        <f>SUMIFS(H2:H48,F2:F48,"単独")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:H48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5563,7 +5927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="2" min="1" max="1"/>
@@ -5571,8 +5935,9 @@
     <col width="52" customWidth="1" style="2" min="3" max="3"/>
     <col width="10" customWidth="1" style="2" min="4" max="4"/>
     <col width="12" customWidth="1" style="2" min="5" max="5"/>
-    <col width="14" customWidth="1" style="2" min="6" max="6"/>
-    <col width="16" customWidth="1" style="2" min="7" max="7"/>
+    <col width="8" customWidth="1" style="2" min="6" max="6"/>
+    <col width="14" customWidth="1" style="2" min="7" max="7"/>
+    <col width="16" customWidth="1" style="2" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5603,10 +5968,15 @@
       </c>
       <c r="F1" s="8" t="inlineStr">
         <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
           <t>在庫数量</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>在庫金額</t>
         </is>
@@ -5639,10 +6009,14 @@
         </is>
       </c>
       <c r="F2" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B2)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G2" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B2,'XTab DS_1'!$D$2:$D$95,$D2)</f>
         <v/>
       </c>
-      <c r="G2" s="11">
+      <c r="H2" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B2,'XTab DS_1'!$D$2:$D$95,$D2)</f>
         <v/>
       </c>
@@ -5674,10 +6048,14 @@
         </is>
       </c>
       <c r="F3" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B3)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G3" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B3,'XTab DS_1'!$D$2:$D$95,$D3)</f>
         <v/>
       </c>
-      <c r="G3" s="11">
+      <c r="H3" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B3,'XTab DS_1'!$D$2:$D$95,$D3)</f>
         <v/>
       </c>
@@ -5709,10 +6087,14 @@
         </is>
       </c>
       <c r="F4" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B4)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G4" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B4,'XTab DS_1'!$D$2:$D$95,$D4)</f>
         <v/>
       </c>
-      <c r="G4" s="11">
+      <c r="H4" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B4,'XTab DS_1'!$D$2:$D$95,$D4)</f>
         <v/>
       </c>
@@ -5744,10 +6126,14 @@
         </is>
       </c>
       <c r="F5" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B5)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G5" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B5,'XTab DS_1'!$D$2:$D$95,$D5)</f>
         <v/>
       </c>
-      <c r="G5" s="11">
+      <c r="H5" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B5,'XTab DS_1'!$D$2:$D$95,$D5)</f>
         <v/>
       </c>
@@ -5779,10 +6165,14 @@
         </is>
       </c>
       <c r="F6" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B6)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G6" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B6,'XTab DS_1'!$D$2:$D$95,$D6)</f>
         <v/>
       </c>
-      <c r="G6" s="11">
+      <c r="H6" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B6,'XTab DS_1'!$D$2:$D$95,$D6)</f>
         <v/>
       </c>
@@ -5814,10 +6204,14 @@
         </is>
       </c>
       <c r="F7" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B7)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G7" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B7,'XTab DS_1'!$D$2:$D$95,$D7)</f>
         <v/>
       </c>
-      <c r="G7" s="11">
+      <c r="H7" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B7,'XTab DS_1'!$D$2:$D$95,$D7)</f>
         <v/>
       </c>
@@ -5849,10 +6243,14 @@
         </is>
       </c>
       <c r="F8" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B8)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G8" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B8,'XTab DS_1'!$D$2:$D$95,$D8)</f>
         <v/>
       </c>
-      <c r="G8" s="11">
+      <c r="H8" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B8,'XTab DS_1'!$D$2:$D$95,$D8)</f>
         <v/>
       </c>
@@ -5884,10 +6282,14 @@
         </is>
       </c>
       <c r="F9" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B9)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G9" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B9,'XTab DS_1'!$D$2:$D$95,$D9)</f>
         <v/>
       </c>
-      <c r="G9" s="11">
+      <c r="H9" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B9,'XTab DS_1'!$D$2:$D$95,$D9)</f>
         <v/>
       </c>
@@ -5919,10 +6321,14 @@
         </is>
       </c>
       <c r="F10" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B10)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G10" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B10,'XTab DS_1'!$D$2:$D$95,$D10)</f>
         <v/>
       </c>
-      <c r="G10" s="11">
+      <c r="H10" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B10,'XTab DS_1'!$D$2:$D$95,$D10)</f>
         <v/>
       </c>
@@ -5954,10 +6360,14 @@
         </is>
       </c>
       <c r="F11" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B11)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G11" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B11,'XTab DS_1'!$D$2:$D$95,$D11)</f>
         <v/>
       </c>
-      <c r="G11" s="11">
+      <c r="H11" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B11,'XTab DS_1'!$D$2:$D$95,$D11)</f>
         <v/>
       </c>
@@ -5989,10 +6399,14 @@
         </is>
       </c>
       <c r="F12" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B12)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G12" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B12,'XTab DS_1'!$D$2:$D$95,$D12)</f>
         <v/>
       </c>
-      <c r="G12" s="11">
+      <c r="H12" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B12,'XTab DS_1'!$D$2:$D$95,$D12)</f>
         <v/>
       </c>
@@ -6024,10 +6438,14 @@
         </is>
       </c>
       <c r="F13" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B13)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G13" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B13,'XTab DS_1'!$D$2:$D$95,$D13)</f>
         <v/>
       </c>
-      <c r="G13" s="11">
+      <c r="H13" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B13,'XTab DS_1'!$D$2:$D$95,$D13)</f>
         <v/>
       </c>
@@ -6059,10 +6477,14 @@
         </is>
       </c>
       <c r="F14" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B14)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G14" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B14,'XTab DS_1'!$D$2:$D$95,$D14)</f>
         <v/>
       </c>
-      <c r="G14" s="11">
+      <c r="H14" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B14,'XTab DS_1'!$D$2:$D$95,$D14)</f>
         <v/>
       </c>
@@ -6094,10 +6516,14 @@
         </is>
       </c>
       <c r="F15" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B15)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G15" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B15,'XTab DS_1'!$D$2:$D$95,$D15)</f>
         <v/>
       </c>
-      <c r="G15" s="11">
+      <c r="H15" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B15,'XTab DS_1'!$D$2:$D$95,$D15)</f>
         <v/>
       </c>
@@ -6129,10 +6555,14 @@
         </is>
       </c>
       <c r="F16" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B16)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G16" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B16,'XTab DS_1'!$D$2:$D$95,$D16)</f>
         <v/>
       </c>
-      <c r="G16" s="11">
+      <c r="H16" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B16,'XTab DS_1'!$D$2:$D$95,$D16)</f>
         <v/>
       </c>
@@ -6164,10 +6594,14 @@
         </is>
       </c>
       <c r="F17" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B17)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G17" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B17,'XTab DS_1'!$D$2:$D$95,$D17)</f>
         <v/>
       </c>
-      <c r="G17" s="11">
+      <c r="H17" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B17,'XTab DS_1'!$D$2:$D$95,$D17)</f>
         <v/>
       </c>
@@ -6199,10 +6633,14 @@
         </is>
       </c>
       <c r="F18" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B18)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G18" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B18,'XTab DS_1'!$D$2:$D$95,$D18)</f>
         <v/>
       </c>
-      <c r="G18" s="11">
+      <c r="H18" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B18,'XTab DS_1'!$D$2:$D$95,$D18)</f>
         <v/>
       </c>
@@ -6234,10 +6672,14 @@
         </is>
       </c>
       <c r="F19" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B19)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G19" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B19,'XTab DS_1'!$D$2:$D$95,$D19)</f>
         <v/>
       </c>
-      <c r="G19" s="11">
+      <c r="H19" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B19,'XTab DS_1'!$D$2:$D$95,$D19)</f>
         <v/>
       </c>
@@ -6269,10 +6711,14 @@
         </is>
       </c>
       <c r="F20" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B20)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G20" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B20,'XTab DS_1'!$D$2:$D$95,$D20)</f>
         <v/>
       </c>
-      <c r="G20" s="11">
+      <c r="H20" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B20,'XTab DS_1'!$D$2:$D$95,$D20)</f>
         <v/>
       </c>
@@ -6304,10 +6750,14 @@
         </is>
       </c>
       <c r="F21" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B21)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G21" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B21,'XTab DS_1'!$D$2:$D$95,$D21)</f>
         <v/>
       </c>
-      <c r="G21" s="11">
+      <c r="H21" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B21,'XTab DS_1'!$D$2:$D$95,$D21)</f>
         <v/>
       </c>
@@ -6339,10 +6789,14 @@
         </is>
       </c>
       <c r="F22" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B22)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G22" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B22,'XTab DS_1'!$D$2:$D$95,$D22)</f>
         <v/>
       </c>
-      <c r="G22" s="11">
+      <c r="H22" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B22,'XTab DS_1'!$D$2:$D$95,$D22)</f>
         <v/>
       </c>
@@ -6374,10 +6828,14 @@
         </is>
       </c>
       <c r="F23" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B23)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G23" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B23,'XTab DS_1'!$D$2:$D$95,$D23)</f>
         <v/>
       </c>
-      <c r="G23" s="11">
+      <c r="H23" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B23,'XTab DS_1'!$D$2:$D$95,$D23)</f>
         <v/>
       </c>
@@ -6409,10 +6867,14 @@
         </is>
       </c>
       <c r="F24" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B24)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G24" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B24,'XTab DS_1'!$D$2:$D$95,$D24)</f>
         <v/>
       </c>
-      <c r="G24" s="11">
+      <c r="H24" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B24,'XTab DS_1'!$D$2:$D$95,$D24)</f>
         <v/>
       </c>
@@ -6444,10 +6906,14 @@
         </is>
       </c>
       <c r="F25" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B25)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G25" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B25,'XTab DS_1'!$D$2:$D$95,$D25)</f>
         <v/>
       </c>
-      <c r="G25" s="11">
+      <c r="H25" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B25,'XTab DS_1'!$D$2:$D$95,$D25)</f>
         <v/>
       </c>
@@ -6479,10 +6945,14 @@
         </is>
       </c>
       <c r="F26" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B26)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G26" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B26,'XTab DS_1'!$D$2:$D$95,$D26)</f>
         <v/>
       </c>
-      <c r="G26" s="11">
+      <c r="H26" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B26,'XTab DS_1'!$D$2:$D$95,$D26)</f>
         <v/>
       </c>
@@ -6514,10 +6984,14 @@
         </is>
       </c>
       <c r="F27" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B27)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G27" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B27,'XTab DS_1'!$D$2:$D$95,$D27)</f>
         <v/>
       </c>
-      <c r="G27" s="11">
+      <c r="H27" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B27,'XTab DS_1'!$D$2:$D$95,$D27)</f>
         <v/>
       </c>
@@ -6549,10 +7023,14 @@
         </is>
       </c>
       <c r="F28" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B28)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G28" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B28,'XTab DS_1'!$D$2:$D$95,$D28)</f>
         <v/>
       </c>
-      <c r="G28" s="11">
+      <c r="H28" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B28,'XTab DS_1'!$D$2:$D$95,$D28)</f>
         <v/>
       </c>
@@ -6584,10 +7062,14 @@
         </is>
       </c>
       <c r="F29" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B29)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G29" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B29,'XTab DS_1'!$D$2:$D$95,$D29)</f>
         <v/>
       </c>
-      <c r="G29" s="11">
+      <c r="H29" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B29,'XTab DS_1'!$D$2:$D$95,$D29)</f>
         <v/>
       </c>
@@ -6619,10 +7101,14 @@
         </is>
       </c>
       <c r="F30" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B30)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G30" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B30,'XTab DS_1'!$D$2:$D$95,$D30)</f>
         <v/>
       </c>
-      <c r="G30" s="11">
+      <c r="H30" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B30,'XTab DS_1'!$D$2:$D$95,$D30)</f>
         <v/>
       </c>
@@ -6654,10 +7140,14 @@
         </is>
       </c>
       <c r="F31" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B31)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G31" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B31,'XTab DS_1'!$D$2:$D$95,$D31)</f>
         <v/>
       </c>
-      <c r="G31" s="11">
+      <c r="H31" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B31,'XTab DS_1'!$D$2:$D$95,$D31)</f>
         <v/>
       </c>
@@ -6689,10 +7179,14 @@
         </is>
       </c>
       <c r="F32" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B32)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G32" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B32,'XTab DS_1'!$D$2:$D$95,$D32)</f>
         <v/>
       </c>
-      <c r="G32" s="11">
+      <c r="H32" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B32,'XTab DS_1'!$D$2:$D$95,$D32)</f>
         <v/>
       </c>
@@ -6724,10 +7218,14 @@
         </is>
       </c>
       <c r="F33" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B33)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G33" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B33,'XTab DS_1'!$D$2:$D$95,$D33)</f>
         <v/>
       </c>
-      <c r="G33" s="11">
+      <c r="H33" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B33,'XTab DS_1'!$D$2:$D$95,$D33)</f>
         <v/>
       </c>
@@ -6759,10 +7257,14 @@
         </is>
       </c>
       <c r="F34" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B34)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G34" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B34,'XTab DS_1'!$D$2:$D$95,$D34)</f>
         <v/>
       </c>
-      <c r="G34" s="11">
+      <c r="H34" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B34,'XTab DS_1'!$D$2:$D$95,$D34)</f>
         <v/>
       </c>
@@ -6794,10 +7296,14 @@
         </is>
       </c>
       <c r="F35" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B35)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G35" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B35,'XTab DS_1'!$D$2:$D$95,$D35)</f>
         <v/>
       </c>
-      <c r="G35" s="11">
+      <c r="H35" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B35,'XTab DS_1'!$D$2:$D$95,$D35)</f>
         <v/>
       </c>
@@ -6829,10 +7335,14 @@
         </is>
       </c>
       <c r="F36" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B36)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G36" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B36,'XTab DS_1'!$D$2:$D$95,$D36)</f>
         <v/>
       </c>
-      <c r="G36" s="11">
+      <c r="H36" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B36,'XTab DS_1'!$D$2:$D$95,$D36)</f>
         <v/>
       </c>
@@ -6864,10 +7374,14 @@
         </is>
       </c>
       <c r="F37" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B37)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G37" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B37,'XTab DS_1'!$D$2:$D$95,$D37)</f>
         <v/>
       </c>
-      <c r="G37" s="11">
+      <c r="H37" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B37,'XTab DS_1'!$D$2:$D$95,$D37)</f>
         <v/>
       </c>
@@ -6899,10 +7413,14 @@
         </is>
       </c>
       <c r="F38" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B38)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G38" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B38,'XTab DS_1'!$D$2:$D$95,$D38)</f>
         <v/>
       </c>
-      <c r="G38" s="11">
+      <c r="H38" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B38,'XTab DS_1'!$D$2:$D$95,$D38)</f>
         <v/>
       </c>
@@ -6934,10 +7452,14 @@
         </is>
       </c>
       <c r="F39" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B39)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G39" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B39,'XTab DS_1'!$D$2:$D$95,$D39)</f>
         <v/>
       </c>
-      <c r="G39" s="11">
+      <c r="H39" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B39,'XTab DS_1'!$D$2:$D$95,$D39)</f>
         <v/>
       </c>
@@ -6969,10 +7491,14 @@
         </is>
       </c>
       <c r="F40" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B40)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G40" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B40,'XTab DS_1'!$D$2:$D$95,$D40)</f>
         <v/>
       </c>
-      <c r="G40" s="11">
+      <c r="H40" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B40,'XTab DS_1'!$D$2:$D$95,$D40)</f>
         <v/>
       </c>
@@ -7004,10 +7530,14 @@
         </is>
       </c>
       <c r="F41" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B41)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G41" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B41,'XTab DS_1'!$D$2:$D$95,$D41)</f>
         <v/>
       </c>
-      <c r="G41" s="11">
+      <c r="H41" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B41,'XTab DS_1'!$D$2:$D$95,$D41)</f>
         <v/>
       </c>
@@ -7039,10 +7569,14 @@
         </is>
       </c>
       <c r="F42" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B42)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G42" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B42,'XTab DS_1'!$D$2:$D$95,$D42)</f>
         <v/>
       </c>
-      <c r="G42" s="11">
+      <c r="H42" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B42,'XTab DS_1'!$D$2:$D$95,$D42)</f>
         <v/>
       </c>
@@ -7074,10 +7608,14 @@
         </is>
       </c>
       <c r="F43" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B43)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G43" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B43,'XTab DS_1'!$D$2:$D$95,$D43)</f>
         <v/>
       </c>
-      <c r="G43" s="11">
+      <c r="H43" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B43,'XTab DS_1'!$D$2:$D$95,$D43)</f>
         <v/>
       </c>
@@ -7109,35 +7647,80 @@
         </is>
       </c>
       <c r="F44" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B44)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G44" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B44,'XTab DS_1'!$D$2:$D$95,$D44)</f>
         <v/>
       </c>
-      <c r="G44" s="11">
+      <c r="H44" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B44,'XTab DS_1'!$D$2:$D$95,$D44)</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="12" t="n"/>
-      <c r="B45" s="12" t="n"/>
-      <c r="C45" s="13" t="inlineStr">
+      <c r="A45" s="17" t="n"/>
+      <c r="B45" s="17" t="n"/>
+      <c r="C45" s="18" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="D45" s="12" t="n"/>
-      <c r="E45" s="12" t="n"/>
-      <c r="F45" s="14">
-        <f>SUM(F2:F44)</f>
-        <v/>
-      </c>
-      <c r="G45" s="15">
+      <c r="D45" s="17" t="n"/>
+      <c r="E45" s="17" t="n"/>
+      <c r="F45" s="17" t="n"/>
+      <c r="G45" s="19">
         <f>SUM(G2:G44)</f>
         <v/>
       </c>
+      <c r="H45" s="20">
+        <f>SUM(H2:H44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="21" t="n"/>
+      <c r="B46" s="21" t="n"/>
+      <c r="C46" s="22" t="inlineStr">
+        <is>
+          <t>うち 重複</t>
+        </is>
+      </c>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="21" t="n"/>
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="23">
+        <f>SUMIFS(G2:G44,F2:F44,"重複")</f>
+        <v/>
+      </c>
+      <c r="H46" s="24">
+        <f>SUMIFS(H2:H44,F2:F44,"重複")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="21" t="n"/>
+      <c r="B47" s="21" t="n"/>
+      <c r="C47" s="22" t="inlineStr">
+        <is>
+          <t>うち 単独</t>
+        </is>
+      </c>
+      <c r="D47" s="21" t="n"/>
+      <c r="E47" s="21" t="n"/>
+      <c r="F47" s="21" t="n"/>
+      <c r="G47" s="23">
+        <f>SUMIFS(G2:G44,F2:F44,"単独")</f>
+        <v/>
+      </c>
+      <c r="H47" s="24">
+        <f>SUMIFS(H2:H44,F2:F44,"単独")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:H44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7148,7 +7731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="2" min="1" max="1"/>
@@ -7156,8 +7739,9 @@
     <col width="52" customWidth="1" style="2" min="3" max="3"/>
     <col width="10" customWidth="1" style="2" min="4" max="4"/>
     <col width="12" customWidth="1" style="2" min="5" max="5"/>
-    <col width="14" customWidth="1" style="2" min="6" max="6"/>
-    <col width="16" customWidth="1" style="2" min="7" max="7"/>
+    <col width="8" customWidth="1" style="2" min="6" max="6"/>
+    <col width="14" customWidth="1" style="2" min="7" max="7"/>
+    <col width="16" customWidth="1" style="2" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7188,10 +7772,15 @@
       </c>
       <c r="F1" s="8" t="inlineStr">
         <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
           <t>在庫数量</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>在庫金額</t>
         </is>
@@ -7224,10 +7813,14 @@
         </is>
       </c>
       <c r="F2" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B2)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G2" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B2,'XTab DS_1'!$D$2:$D$95,$D2)</f>
         <v/>
       </c>
-      <c r="G2" s="11">
+      <c r="H2" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B2,'XTab DS_1'!$D$2:$D$95,$D2)</f>
         <v/>
       </c>
@@ -7259,10 +7852,14 @@
         </is>
       </c>
       <c r="F3" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B3)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G3" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B3,'XTab DS_1'!$D$2:$D$95,$D3)</f>
         <v/>
       </c>
-      <c r="G3" s="11">
+      <c r="H3" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B3,'XTab DS_1'!$D$2:$D$95,$D3)</f>
         <v/>
       </c>
@@ -7294,10 +7891,14 @@
         </is>
       </c>
       <c r="F4" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B4)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G4" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B4,'XTab DS_1'!$D$2:$D$95,$D4)</f>
         <v/>
       </c>
-      <c r="G4" s="11">
+      <c r="H4" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B4,'XTab DS_1'!$D$2:$D$95,$D4)</f>
         <v/>
       </c>
@@ -7329,35 +7930,80 @@
         </is>
       </c>
       <c r="F5" s="10">
+        <f>IF(COUNTIFS('XTab DS_1'!$B$2:$B$95,$B5)&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="G5" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B5,'XTab DS_1'!$D$2:$D$95,$D5)</f>
         <v/>
       </c>
-      <c r="G5" s="11">
+      <c r="H5" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B5,'XTab DS_1'!$D$2:$D$95,$D5)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="n"/>
-      <c r="B6" s="12" t="n"/>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="A6" s="17" t="n"/>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="14">
-        <f>SUM(F2:F5)</f>
-        <v/>
-      </c>
-      <c r="G6" s="15">
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+      <c r="G6" s="19">
         <f>SUM(G2:G5)</f>
         <v/>
       </c>
+      <c r="H6" s="20">
+        <f>SUM(H2:H5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="n"/>
+      <c r="B7" s="21" t="n"/>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>うち 重複</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="n"/>
+      <c r="E7" s="21" t="n"/>
+      <c r="F7" s="21" t="n"/>
+      <c r="G7" s="23">
+        <f>SUMIFS(G2:G5,F2:F5,"重複")</f>
+        <v/>
+      </c>
+      <c r="H7" s="24">
+        <f>SUMIFS(H2:H5,F2:F5,"重複")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="n"/>
+      <c r="B8" s="21" t="n"/>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>うち 単独</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="n"/>
+      <c r="E8" s="21" t="n"/>
+      <c r="F8" s="21" t="n"/>
+      <c r="G8" s="23">
+        <f>SUMIFS(G2:G5,F2:F5,"単独")</f>
+        <v/>
+      </c>
+      <c r="H8" s="24">
+        <f>SUMIFS(H2:H5,F2:F5,"単独")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:H5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7368,21 +8014,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="2" min="1" max="1"/>
     <col width="24" customWidth="1" style="2" min="2" max="2"/>
     <col width="52" customWidth="1" style="2" min="3" max="3"/>
     <col width="10" customWidth="1" style="2" min="4" max="4"/>
-    <col width="13" customWidth="1" style="2" min="5" max="5"/>
-    <col width="14" customWidth="1" style="2" min="6" max="6"/>
-    <col width="13" customWidth="1" style="2" min="7" max="7"/>
-    <col width="14" customWidth="1" style="2" min="8" max="8"/>
-    <col width="13" customWidth="1" style="2" min="9" max="9"/>
-    <col width="14" customWidth="1" style="2" min="10" max="10"/>
-    <col width="15" customWidth="1" style="2" min="11" max="11"/>
-    <col width="18" customWidth="1" style="2" min="12" max="12"/>
+    <col width="8" customWidth="1" style="2" min="5" max="5"/>
+    <col width="13" customWidth="1" style="2" min="6" max="6"/>
+    <col width="14" customWidth="1" style="2" min="7" max="7"/>
+    <col width="13" customWidth="1" style="2" min="8" max="8"/>
+    <col width="14" customWidth="1" style="2" min="9" max="9"/>
+    <col width="13" customWidth="1" style="2" min="10" max="10"/>
+    <col width="14" customWidth="1" style="2" min="11" max="11"/>
+    <col width="15" customWidth="1" style="2" min="12" max="12"/>
+    <col width="18" customWidth="1" style="2" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7403,45 +8050,50 @@
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>重複倉庫数</t>
+          <t>登録倉庫数</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
         <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
           <t>CX催事 数量</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>CX催事 金額</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>DBS倉庫 数量</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>DBS倉庫 金額</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>その他 数量</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>その他 金額</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="L1" s="8" t="inlineStr">
         <is>
           <t>合算 在庫数量</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="M1" s="8" t="inlineStr">
         <is>
           <t>合算 在庫金額(原価)</t>
         </is>
@@ -7463,39 +8115,43 @@
           <t>呪術廻戦展 懐玉玉折 渋谷事変　メタリックポストカード　展示会KV</t>
         </is>
       </c>
-      <c r="D2" s="16">
+      <c r="D2" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B2)</f>
         <v/>
       </c>
       <c r="E2" s="10">
+        <f>IF(D2&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F2" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B2,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F2" s="11">
+      <c r="G2" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B2,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G2" s="10">
+      <c r="H2" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B2,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H2" s="11">
+      <c r="I2" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B2,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I2" s="10">
+      <c r="J2" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B2,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J2" s="11">
+      <c r="K2" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B2,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K2" s="17">
+      <c r="L2" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B2)</f>
         <v/>
       </c>
-      <c r="L2" s="18">
+      <c r="M2" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B2)</f>
         <v/>
       </c>
@@ -7516,39 +8172,43 @@
           <t>呪術廻戦展 懐玉玉折 渋谷事変　クリアファイル　展示会KV</t>
         </is>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B3)</f>
         <v/>
       </c>
       <c r="E3" s="10">
+        <f>IF(D3&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F3" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B3,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F3" s="11">
+      <c r="G3" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B3,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G3" s="10">
+      <c r="H3" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B3,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H3" s="11">
+      <c r="I3" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B3,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I3" s="10">
+      <c r="J3" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B3,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J3" s="11">
+      <c r="K3" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B3,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K3" s="17">
+      <c r="L3" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B3)</f>
         <v/>
       </c>
-      <c r="L3" s="18">
+      <c r="M3" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B3)</f>
         <v/>
       </c>
@@ -7569,39 +8229,43 @@
           <t>呪術廻戦展 懐玉玉折　ポストカードセット（5枚入）</t>
         </is>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B4)</f>
         <v/>
       </c>
       <c r="E4" s="10">
+        <f>IF(D4&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F4" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B4,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F4" s="11">
+      <c r="G4" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B4,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G4" s="10">
+      <c r="H4" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B4,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H4" s="11">
+      <c r="I4" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B4,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I4" s="10">
+      <c r="J4" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B4,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J4" s="11">
+      <c r="K4" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B4,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K4" s="17">
+      <c r="L4" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B4)</f>
         <v/>
       </c>
-      <c r="L4" s="18">
+      <c r="M4" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B4)</f>
         <v/>
       </c>
@@ -7622,39 +8286,43 @@
           <t>呪術廻戦展 渋谷事変　ポストカードセット（9枚入）</t>
         </is>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B5)</f>
         <v/>
       </c>
       <c r="E5" s="10">
+        <f>IF(D5&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F5" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B5,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F5" s="11">
+      <c r="G5" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B5,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G5" s="10">
+      <c r="H5" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B5,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H5" s="11">
+      <c r="I5" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B5,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I5" s="10">
+      <c r="J5" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B5,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J5" s="11">
+      <c r="K5" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B5,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K5" s="17">
+      <c r="L5" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B5)</f>
         <v/>
       </c>
-      <c r="L5" s="18">
+      <c r="M5" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B5)</f>
         <v/>
       </c>
@@ -7675,39 +8343,43 @@
           <t>呪術廻戦展 懐玉玉折　ブラインド缶バッジ（全5種）</t>
         </is>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B6)</f>
         <v/>
       </c>
       <c r="E6" s="10">
+        <f>IF(D6&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F6" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B6,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F6" s="11">
+      <c r="G6" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B6,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G6" s="10">
+      <c r="H6" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B6,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H6" s="11">
+      <c r="I6" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B6,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I6" s="10">
+      <c r="J6" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B6,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J6" s="11">
+      <c r="K6" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B6,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K6" s="17">
+      <c r="L6" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B6)</f>
         <v/>
       </c>
-      <c r="L6" s="18">
+      <c r="M6" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B6)</f>
         <v/>
       </c>
@@ -7728,39 +8400,43 @@
           <t>呪術廻戦展 渋谷事変　ブラインド缶バッジ（全9種）</t>
         </is>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B7)</f>
         <v/>
       </c>
       <c r="E7" s="10">
+        <f>IF(D7&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F7" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B7,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F7" s="11">
+      <c r="G7" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B7,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G7" s="10">
+      <c r="H7" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B7,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H7" s="11">
+      <c r="I7" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B7,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I7" s="10">
+      <c r="J7" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B7,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J7" s="11">
+      <c r="K7" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B7,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K7" s="17">
+      <c r="L7" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B7)</f>
         <v/>
       </c>
-      <c r="L7" s="18">
+      <c r="M7" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B7)</f>
         <v/>
       </c>
@@ -7781,39 +8457,43 @@
           <t>呪術廻戦展 懐玉玉折　ブラインドダイカットステッカー（全5種）</t>
         </is>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B8)</f>
         <v/>
       </c>
       <c r="E8" s="10">
+        <f>IF(D8&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F8" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B8,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F8" s="11">
+      <c r="G8" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B8,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G8" s="10">
+      <c r="H8" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B8,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H8" s="11">
+      <c r="I8" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B8,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I8" s="10">
+      <c r="J8" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B8,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J8" s="11">
+      <c r="K8" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B8,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K8" s="17">
+      <c r="L8" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B8)</f>
         <v/>
       </c>
-      <c r="L8" s="18">
+      <c r="M8" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B8)</f>
         <v/>
       </c>
@@ -7834,39 +8514,43 @@
           <t>呪術廻戦展 渋谷事変　ブラインドダイカットステッカー（全9種）</t>
         </is>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B9)</f>
         <v/>
       </c>
       <c r="E9" s="10">
+        <f>IF(D9&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F9" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B9,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F9" s="11">
+      <c r="G9" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B9,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G9" s="10">
+      <c r="H9" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B9,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H9" s="11">
+      <c r="I9" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B9,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I9" s="10">
+      <c r="J9" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B9,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J9" s="11">
+      <c r="K9" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B9,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K9" s="17">
+      <c r="L9" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B9)</f>
         <v/>
       </c>
-      <c r="L9" s="18">
+      <c r="M9" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B9)</f>
         <v/>
       </c>
@@ -7887,39 +8571,43 @@
           <t>呪術廻戦展 懐玉玉折　ブラインドミニ色紙（全5種）</t>
         </is>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B10)</f>
         <v/>
       </c>
       <c r="E10" s="10">
+        <f>IF(D10&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F10" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B10,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F10" s="11">
+      <c r="G10" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B10,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G10" s="10">
+      <c r="H10" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B10,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H10" s="11">
+      <c r="I10" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B10,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I10" s="10">
+      <c r="J10" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B10,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J10" s="11">
+      <c r="K10" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B10,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K10" s="17">
+      <c r="L10" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B10)</f>
         <v/>
       </c>
-      <c r="L10" s="18">
+      <c r="M10" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B10)</f>
         <v/>
       </c>
@@ -7940,39 +8628,43 @@
           <t>呪術廻戦展 渋谷事変　ブラインドミニ色紙（全5種）</t>
         </is>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B11)</f>
         <v/>
       </c>
       <c r="E11" s="10">
+        <f>IF(D11&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F11" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B11,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F11" s="11">
+      <c r="G11" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B11,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G11" s="10">
+      <c r="H11" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B11,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H11" s="11">
+      <c r="I11" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B11,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I11" s="10">
+      <c r="J11" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B11,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J11" s="11">
+      <c r="K11" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B11,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K11" s="17">
+      <c r="L11" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B11)</f>
         <v/>
       </c>
-      <c r="L11" s="18">
+      <c r="M11" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B11)</f>
         <v/>
       </c>
@@ -7993,39 +8685,43 @@
           <t>呪術廻戦展 懐玉玉折 渋谷事変　虚式 ? バスボール</t>
         </is>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B12)</f>
         <v/>
       </c>
       <c r="E12" s="10">
+        <f>IF(D12&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F12" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B12,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F12" s="11">
+      <c r="G12" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B12,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G12" s="10">
+      <c r="H12" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B12,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H12" s="11">
+      <c r="I12" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B12,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I12" s="10">
+      <c r="J12" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B12,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J12" s="11">
+      <c r="K12" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B12,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K12" s="17">
+      <c r="L12" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B12)</f>
         <v/>
       </c>
-      <c r="L12" s="18">
+      <c r="M12" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B12)</f>
         <v/>
       </c>
@@ -8046,39 +8742,43 @@
           <t>呪術廻戦展 懐玉玉折 渋谷事変　前髪ヘアバンド</t>
         </is>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B13)</f>
         <v/>
       </c>
       <c r="E13" s="10">
+        <f>IF(D13&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F13" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B13,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F13" s="11">
+      <c r="G13" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B13,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G13" s="10">
+      <c r="H13" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B13,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H13" s="11">
+      <c r="I13" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B13,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I13" s="10">
+      <c r="J13" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B13,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J13" s="11">
+      <c r="K13" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B13,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K13" s="17">
+      <c r="L13" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B13)</f>
         <v/>
       </c>
-      <c r="L13" s="18">
+      <c r="M13" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B13)</f>
         <v/>
       </c>
@@ -8099,39 +8799,43 @@
           <t>呪術廻戦展 懐玉玉折 渋谷事変　反転術式絆創膏</t>
         </is>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B14)</f>
         <v/>
       </c>
       <c r="E14" s="10">
+        <f>IF(D14&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F14" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B14,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F14" s="11">
+      <c r="G14" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B14,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G14" s="10">
+      <c r="H14" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B14,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H14" s="11">
+      <c r="I14" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B14,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I14" s="10">
+      <c r="J14" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B14,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J14" s="11">
+      <c r="K14" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B14,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K14" s="17">
+      <c r="L14" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B14)</f>
         <v/>
       </c>
-      <c r="L14" s="18">
+      <c r="M14" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B14)</f>
         <v/>
       </c>
@@ -8152,39 +8856,43 @@
           <t>呪術廻戦展 懐玉玉折 渋谷事変　宿儺の指風お菓子</t>
         </is>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B15)</f>
         <v/>
       </c>
       <c r="E15" s="10">
+        <f>IF(D15&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F15" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B15,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F15" s="11">
+      <c r="G15" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B15,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G15" s="10">
+      <c r="H15" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B15,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H15" s="11">
+      <c r="I15" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B15,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I15" s="10">
+      <c r="J15" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B15,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J15" s="11">
+      <c r="K15" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B15,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K15" s="17">
+      <c r="L15" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B15)</f>
         <v/>
       </c>
-      <c r="L15" s="18">
+      <c r="M15" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B15)</f>
         <v/>
       </c>
@@ -8205,39 +8913,43 @@
           <t>呪術廻戦展 懐玉玉折 渋谷事変　脱兎 ポーチ入りクリップセット</t>
         </is>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B16)</f>
         <v/>
       </c>
       <c r="E16" s="10">
+        <f>IF(D16&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F16" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B16,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F16" s="11">
+      <c r="G16" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B16,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G16" s="10">
+      <c r="H16" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B16,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H16" s="11">
+      <c r="I16" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B16,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I16" s="10">
+      <c r="J16" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B16,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J16" s="11">
+      <c r="K16" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B16,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K16" s="17">
+      <c r="L16" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B16)</f>
         <v/>
       </c>
-      <c r="L16" s="18">
+      <c r="M16" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B16)</f>
         <v/>
       </c>
@@ -8258,39 +8970,43 @@
           <t>呪術廻戦展 懐玉玉折 渋谷事変　釘崎のポーチ風エコバッグ</t>
         </is>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B17)</f>
         <v/>
       </c>
       <c r="E17" s="10">
+        <f>IF(D17&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F17" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B17,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F17" s="11">
+      <c r="G17" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B17,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G17" s="10">
+      <c r="H17" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B17,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H17" s="11">
+      <c r="I17" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B17,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I17" s="10">
+      <c r="J17" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B17,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J17" s="11">
+      <c r="K17" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B17,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K17" s="17">
+      <c r="L17" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B17)</f>
         <v/>
       </c>
-      <c r="L17" s="18">
+      <c r="M17" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B17)</f>
         <v/>
       </c>
@@ -8311,39 +9027,43 @@
           <t>呪術廻戦展 懐玉玉折 渋谷事変　半年分の情報が書き込める手帳</t>
         </is>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B18)</f>
         <v/>
       </c>
       <c r="E18" s="10">
+        <f>IF(D18&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F18" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B18,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F18" s="11">
+      <c r="G18" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B18,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G18" s="10">
+      <c r="H18" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B18,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H18" s="11">
+      <c r="I18" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B18,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I18" s="10">
+      <c r="J18" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B18,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J18" s="11">
+      <c r="K18" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B18,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K18" s="17">
+      <c r="L18" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B18)</f>
         <v/>
       </c>
-      <c r="L18" s="18">
+      <c r="M18" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B18)</f>
         <v/>
       </c>
@@ -8364,39 +9084,43 @@
           <t>呪術廻戦展 懐玉玉折 渋谷事変　気分リフレッシュオルゴール</t>
         </is>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B19)</f>
         <v/>
       </c>
       <c r="E19" s="10">
+        <f>IF(D19&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F19" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B19,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F19" s="11">
+      <c r="G19" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B19,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G19" s="10">
+      <c r="H19" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B19,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H19" s="11">
+      <c r="I19" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B19,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I19" s="10">
+      <c r="J19" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B19,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J19" s="11">
+      <c r="K19" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B19,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K19" s="17">
+      <c r="L19" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B19)</f>
         <v/>
       </c>
-      <c r="L19" s="18">
+      <c r="M19" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B19)</f>
         <v/>
       </c>
@@ -8417,39 +9141,43 @@
           <t>呪術廻戦展 懐玉玉折 渋谷事変　五条 悟　イメージリング（#11）</t>
         </is>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B20)</f>
         <v/>
       </c>
       <c r="E20" s="10">
+        <f>IF(D20&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F20" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B20,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F20" s="11">
+      <c r="G20" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B20,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G20" s="10">
+      <c r="H20" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B20,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H20" s="11">
+      <c r="I20" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B20,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I20" s="10">
+      <c r="J20" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B20,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J20" s="11">
+      <c r="K20" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B20,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K20" s="17">
+      <c r="L20" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B20)</f>
         <v/>
       </c>
-      <c r="L20" s="18">
+      <c r="M20" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B20)</f>
         <v/>
       </c>
@@ -8470,39 +9198,43 @@
           <t>呪術廻戦展 懐玉玉折 渋谷事変　五条 悟　イメージリング（#13）</t>
         </is>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B21)</f>
         <v/>
       </c>
       <c r="E21" s="10">
+        <f>IF(D21&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F21" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B21,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F21" s="11">
+      <c r="G21" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B21,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G21" s="10">
+      <c r="H21" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B21,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H21" s="11">
+      <c r="I21" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B21,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I21" s="10">
+      <c r="J21" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B21,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J21" s="11">
+      <c r="K21" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B21,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K21" s="17">
+      <c r="L21" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B21)</f>
         <v/>
       </c>
-      <c r="L21" s="18">
+      <c r="M21" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B21)</f>
         <v/>
       </c>
@@ -8523,39 +9255,43 @@
           <t>呪術廻戦展 懐玉玉折 渋谷事変　五条 悟　イメージリング（#15）</t>
         </is>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B22)</f>
         <v/>
       </c>
       <c r="E22" s="10">
+        <f>IF(D22&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F22" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B22,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F22" s="11">
+      <c r="G22" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B22,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G22" s="10">
+      <c r="H22" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B22,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H22" s="11">
+      <c r="I22" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B22,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I22" s="10">
+      <c r="J22" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B22,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J22" s="11">
+      <c r="K22" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B22,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K22" s="17">
+      <c r="L22" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B22)</f>
         <v/>
       </c>
-      <c r="L22" s="18">
+      <c r="M22" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B22)</f>
         <v/>
       </c>
@@ -8576,39 +9312,43 @@
           <t>呪術廻戦展 懐玉玉折 渋谷事変　五条 悟　イメージリング（#17）</t>
         </is>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B23)</f>
         <v/>
       </c>
       <c r="E23" s="10">
+        <f>IF(D23&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F23" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B23,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F23" s="11">
+      <c r="G23" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B23,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G23" s="10">
+      <c r="H23" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B23,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H23" s="11">
+      <c r="I23" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B23,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I23" s="10">
+      <c r="J23" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B23,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J23" s="11">
+      <c r="K23" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B23,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K23" s="17">
+      <c r="L23" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B23)</f>
         <v/>
       </c>
-      <c r="L23" s="18">
+      <c r="M23" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B23)</f>
         <v/>
       </c>
@@ -8629,39 +9369,43 @@
           <t>呪術廻戦展 懐玉玉折 渋谷事変　夏油 傑　イメージリング（#11）</t>
         </is>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B24)</f>
         <v/>
       </c>
       <c r="E24" s="10">
+        <f>IF(D24&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F24" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B24,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F24" s="11">
+      <c r="G24" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B24,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G24" s="10">
+      <c r="H24" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B24,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H24" s="11">
+      <c r="I24" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B24,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I24" s="10">
+      <c r="J24" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B24,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J24" s="11">
+      <c r="K24" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B24,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K24" s="17">
+      <c r="L24" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B24)</f>
         <v/>
       </c>
-      <c r="L24" s="18">
+      <c r="M24" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B24)</f>
         <v/>
       </c>
@@ -8682,39 +9426,43 @@
           <t>呪術廻戦展 懐玉玉折 渋谷事変　夏油 傑　イメージリング（#13）</t>
         </is>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B25)</f>
         <v/>
       </c>
       <c r="E25" s="10">
+        <f>IF(D25&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F25" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B25,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F25" s="11">
+      <c r="G25" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B25,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G25" s="10">
+      <c r="H25" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B25,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H25" s="11">
+      <c r="I25" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B25,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I25" s="10">
+      <c r="J25" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B25,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J25" s="11">
+      <c r="K25" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B25,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K25" s="17">
+      <c r="L25" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B25)</f>
         <v/>
       </c>
-      <c r="L25" s="18">
+      <c r="M25" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B25)</f>
         <v/>
       </c>
@@ -8735,39 +9483,43 @@
           <t>呪術廻戦展 懐玉玉折 渋谷事変　夏油 傑　イメージリング（#15）</t>
         </is>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B26)</f>
         <v/>
       </c>
       <c r="E26" s="10">
+        <f>IF(D26&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F26" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B26,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F26" s="11">
+      <c r="G26" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B26,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G26" s="10">
+      <c r="H26" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B26,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H26" s="11">
+      <c r="I26" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B26,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I26" s="10">
+      <c r="J26" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B26,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J26" s="11">
+      <c r="K26" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B26,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K26" s="17">
+      <c r="L26" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B26)</f>
         <v/>
       </c>
-      <c r="L26" s="18">
+      <c r="M26" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B26)</f>
         <v/>
       </c>
@@ -8788,39 +9540,43 @@
           <t>呪術廻戦展 懐玉玉折 渋谷事変　夏油 傑　イメージリング（#17）</t>
         </is>
       </c>
-      <c r="D27" s="16">
+      <c r="D27" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B27)</f>
         <v/>
       </c>
       <c r="E27" s="10">
+        <f>IF(D27&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F27" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B27,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F27" s="11">
+      <c r="G27" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B27,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G27" s="10">
+      <c r="H27" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B27,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H27" s="11">
+      <c r="I27" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B27,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I27" s="10">
+      <c r="J27" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B27,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J27" s="11">
+      <c r="K27" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B27,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K27" s="17">
+      <c r="L27" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B27)</f>
         <v/>
       </c>
-      <c r="L27" s="18">
+      <c r="M27" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B27)</f>
         <v/>
       </c>
@@ -8841,39 +9597,43 @@
           <t>呪術廻戦展 懐玉玉折 渋谷事変　虎杖 悠仁　イメージフラグメントケース</t>
         </is>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B28)</f>
         <v/>
       </c>
       <c r="E28" s="10">
+        <f>IF(D28&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F28" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B28,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F28" s="11">
+      <c r="G28" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B28,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G28" s="10">
+      <c r="H28" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B28,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H28" s="11">
+      <c r="I28" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B28,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I28" s="10">
+      <c r="J28" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B28,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J28" s="11">
+      <c r="K28" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B28,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K28" s="17">
+      <c r="L28" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B28)</f>
         <v/>
       </c>
-      <c r="L28" s="18">
+      <c r="M28" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B28)</f>
         <v/>
       </c>
@@ -8894,39 +9654,43 @@
           <t>呪術廻戦展 懐玉玉折 渋谷事変　伏黒 恵　イメージフラグメントケース</t>
         </is>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B29)</f>
         <v/>
       </c>
       <c r="E29" s="10">
+        <f>IF(D29&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F29" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B29,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F29" s="11">
+      <c r="G29" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B29,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G29" s="10">
+      <c r="H29" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B29,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H29" s="11">
+      <c r="I29" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B29,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I29" s="10">
+      <c r="J29" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B29,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J29" s="11">
+      <c r="K29" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B29,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K29" s="17">
+      <c r="L29" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B29)</f>
         <v/>
       </c>
-      <c r="L29" s="18">
+      <c r="M29" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B29)</f>
         <v/>
       </c>
@@ -8947,39 +9711,43 @@
           <t>呪術廻戦展 懐玉玉折　クリアファイル（五条 悟）</t>
         </is>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B30)</f>
         <v/>
       </c>
       <c r="E30" s="10">
+        <f>IF(D30&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F30" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B30,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F30" s="11">
+      <c r="G30" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B30,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G30" s="10">
+      <c r="H30" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B30,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H30" s="11">
+      <c r="I30" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B30,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I30" s="10">
+      <c r="J30" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B30,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J30" s="11">
+      <c r="K30" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B30,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K30" s="17">
+      <c r="L30" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B30)</f>
         <v/>
       </c>
-      <c r="L30" s="18">
+      <c r="M30" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B30)</f>
         <v/>
       </c>
@@ -9000,39 +9768,43 @@
           <t>呪術廻戦展 懐玉玉折　クリアファイル（夏油 傑）</t>
         </is>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B31)</f>
         <v/>
       </c>
       <c r="E31" s="10">
+        <f>IF(D31&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F31" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B31,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F31" s="11">
+      <c r="G31" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B31,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G31" s="10">
+      <c r="H31" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B31,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H31" s="11">
+      <c r="I31" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B31,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I31" s="10">
+      <c r="J31" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B31,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J31" s="11">
+      <c r="K31" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B31,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K31" s="17">
+      <c r="L31" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B31)</f>
         <v/>
       </c>
-      <c r="L31" s="18">
+      <c r="M31" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B31)</f>
         <v/>
       </c>
@@ -9053,39 +9825,43 @@
           <t>呪術廻戦展 懐玉玉折　クリアファイル（家入 硝子）</t>
         </is>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B32)</f>
         <v/>
       </c>
       <c r="E32" s="10">
+        <f>IF(D32&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F32" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B32,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F32" s="11">
+      <c r="G32" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B32,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G32" s="10">
+      <c r="H32" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B32,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H32" s="11">
+      <c r="I32" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B32,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I32" s="10">
+      <c r="J32" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B32,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J32" s="11">
+      <c r="K32" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B32,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K32" s="17">
+      <c r="L32" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B32)</f>
         <v/>
       </c>
-      <c r="L32" s="18">
+      <c r="M32" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B32)</f>
         <v/>
       </c>
@@ -9106,39 +9882,43 @@
           <t>呪術廻戦展 懐玉玉折　クリアファイル（七海 建人）</t>
         </is>
       </c>
-      <c r="D33" s="16">
+      <c r="D33" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B33)</f>
         <v/>
       </c>
       <c r="E33" s="10">
+        <f>IF(D33&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F33" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B33,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F33" s="11">
+      <c r="G33" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B33,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G33" s="10">
+      <c r="H33" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B33,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H33" s="11">
+      <c r="I33" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B33,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I33" s="10">
+      <c r="J33" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B33,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J33" s="11">
+      <c r="K33" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B33,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K33" s="17">
+      <c r="L33" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B33)</f>
         <v/>
       </c>
-      <c r="L33" s="18">
+      <c r="M33" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B33)</f>
         <v/>
       </c>
@@ -9159,39 +9939,43 @@
           <t>呪術廻戦展 懐玉玉折　クリアファイル（灰原 雄）</t>
         </is>
       </c>
-      <c r="D34" s="16">
+      <c r="D34" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B34)</f>
         <v/>
       </c>
       <c r="E34" s="10">
+        <f>IF(D34&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F34" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B34,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F34" s="11">
+      <c r="G34" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B34,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G34" s="10">
+      <c r="H34" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B34,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H34" s="11">
+      <c r="I34" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B34,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I34" s="10">
+      <c r="J34" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B34,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J34" s="11">
+      <c r="K34" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B34,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K34" s="17">
+      <c r="L34" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B34)</f>
         <v/>
       </c>
-      <c r="L34" s="18">
+      <c r="M34" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B34)</f>
         <v/>
       </c>
@@ -9212,39 +9996,43 @@
           <t>呪術廻戦展 渋谷事変　クリアファイル（虎杖 悠仁）</t>
         </is>
       </c>
-      <c r="D35" s="16">
+      <c r="D35" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B35)</f>
         <v/>
       </c>
       <c r="E35" s="10">
+        <f>IF(D35&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F35" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B35,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F35" s="11">
+      <c r="G35" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B35,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G35" s="10">
+      <c r="H35" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B35,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H35" s="11">
+      <c r="I35" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B35,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I35" s="10">
+      <c r="J35" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B35,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J35" s="11">
+      <c r="K35" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B35,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K35" s="17">
+      <c r="L35" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B35)</f>
         <v/>
       </c>
-      <c r="L35" s="18">
+      <c r="M35" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B35)</f>
         <v/>
       </c>
@@ -9265,39 +10053,43 @@
           <t>呪術廻戦展 渋谷事変　クリアファイル（伏黒 恵）</t>
         </is>
       </c>
-      <c r="D36" s="16">
+      <c r="D36" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B36)</f>
         <v/>
       </c>
       <c r="E36" s="10">
+        <f>IF(D36&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F36" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B36,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F36" s="11">
+      <c r="G36" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B36,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G36" s="10">
+      <c r="H36" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B36,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H36" s="11">
+      <c r="I36" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B36,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I36" s="10">
+      <c r="J36" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B36,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J36" s="11">
+      <c r="K36" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B36,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K36" s="17">
+      <c r="L36" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B36)</f>
         <v/>
       </c>
-      <c r="L36" s="18">
+      <c r="M36" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B36)</f>
         <v/>
       </c>
@@ -9318,39 +10110,43 @@
           <t>呪術廻戦展 渋谷事変　クリアファイル（釘崎 野薔薇）</t>
         </is>
       </c>
-      <c r="D37" s="16">
+      <c r="D37" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B37)</f>
         <v/>
       </c>
       <c r="E37" s="10">
+        <f>IF(D37&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F37" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B37,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F37" s="11">
+      <c r="G37" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B37,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G37" s="10">
+      <c r="H37" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B37,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H37" s="11">
+      <c r="I37" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B37,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I37" s="10">
+      <c r="J37" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B37,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J37" s="11">
+      <c r="K37" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B37,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K37" s="17">
+      <c r="L37" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B37)</f>
         <v/>
       </c>
-      <c r="L37" s="18">
+      <c r="M37" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B37)</f>
         <v/>
       </c>
@@ -9371,39 +10167,43 @@
           <t>呪術廻戦展 渋谷事変　クリアファイル（七海 建人）</t>
         </is>
       </c>
-      <c r="D38" s="16">
+      <c r="D38" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B38)</f>
         <v/>
       </c>
       <c r="E38" s="10">
+        <f>IF(D38&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F38" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B38,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F38" s="11">
+      <c r="G38" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B38,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G38" s="10">
+      <c r="H38" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B38,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H38" s="11">
+      <c r="I38" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B38,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I38" s="10">
+      <c r="J38" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B38,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J38" s="11">
+      <c r="K38" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B38,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K38" s="17">
+      <c r="L38" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B38)</f>
         <v/>
       </c>
-      <c r="L38" s="18">
+      <c r="M38" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B38)</f>
         <v/>
       </c>
@@ -9424,39 +10224,43 @@
           <t>呪術廻戦展 渋谷事変　クリアファイル（五条 悟）</t>
         </is>
       </c>
-      <c r="D39" s="16">
+      <c r="D39" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B39)</f>
         <v/>
       </c>
       <c r="E39" s="10">
+        <f>IF(D39&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F39" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B39,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F39" s="11">
+      <c r="G39" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B39,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G39" s="10">
+      <c r="H39" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B39,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H39" s="11">
+      <c r="I39" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B39,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I39" s="10">
+      <c r="J39" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B39,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J39" s="11">
+      <c r="K39" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B39,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K39" s="17">
+      <c r="L39" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B39)</f>
         <v/>
       </c>
-      <c r="L39" s="18">
+      <c r="M39" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B39)</f>
         <v/>
       </c>
@@ -9477,39 +10281,43 @@
           <t>呪術廻戦展 渋谷事変　クリアファイル（夏油 傑）</t>
         </is>
       </c>
-      <c r="D40" s="16">
+      <c r="D40" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B40)</f>
         <v/>
       </c>
       <c r="E40" s="10">
+        <f>IF(D40&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F40" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B40,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F40" s="11">
+      <c r="G40" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B40,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G40" s="10">
+      <c r="H40" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B40,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H40" s="11">
+      <c r="I40" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B40,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I40" s="10">
+      <c r="J40" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B40,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J40" s="11">
+      <c r="K40" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B40,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K40" s="17">
+      <c r="L40" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B40)</f>
         <v/>
       </c>
-      <c r="L40" s="18">
+      <c r="M40" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B40)</f>
         <v/>
       </c>
@@ -9530,39 +10338,43 @@
           <t>呪術廻戦展 渋谷事変　クリアファイル（真人）</t>
         </is>
       </c>
-      <c r="D41" s="16">
+      <c r="D41" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B41)</f>
         <v/>
       </c>
       <c r="E41" s="10">
+        <f>IF(D41&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F41" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B41,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F41" s="11">
+      <c r="G41" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B41,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G41" s="10">
+      <c r="H41" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B41,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H41" s="11">
+      <c r="I41" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B41,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I41" s="10">
+      <c r="J41" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B41,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J41" s="11">
+      <c r="K41" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B41,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K41" s="17">
+      <c r="L41" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B41)</f>
         <v/>
       </c>
-      <c r="L41" s="18">
+      <c r="M41" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B41)</f>
         <v/>
       </c>
@@ -9583,39 +10395,43 @@
           <t>呪術廻戦展 渋谷事変　クリアファイル（脹相）</t>
         </is>
       </c>
-      <c r="D42" s="16">
+      <c r="D42" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B42)</f>
         <v/>
       </c>
       <c r="E42" s="10">
+        <f>IF(D42&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F42" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B42,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F42" s="11">
+      <c r="G42" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B42,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G42" s="10">
+      <c r="H42" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B42,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H42" s="11">
+      <c r="I42" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B42,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I42" s="10">
+      <c r="J42" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B42,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J42" s="11">
+      <c r="K42" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B42,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K42" s="17">
+      <c r="L42" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B42)</f>
         <v/>
       </c>
-      <c r="L42" s="18">
+      <c r="M42" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B42)</f>
         <v/>
       </c>
@@ -9636,39 +10452,43 @@
           <t>呪術廻戦展 渋谷事変　クリアファイル（宿儺）</t>
         </is>
       </c>
-      <c r="D43" s="16">
+      <c r="D43" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B43)</f>
         <v/>
       </c>
       <c r="E43" s="10">
+        <f>IF(D43&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F43" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B43,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F43" s="11">
+      <c r="G43" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B43,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G43" s="10">
+      <c r="H43" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B43,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H43" s="11">
+      <c r="I43" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B43,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I43" s="10">
+      <c r="J43" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B43,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J43" s="11">
+      <c r="K43" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B43,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K43" s="17">
+      <c r="L43" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B43)</f>
         <v/>
       </c>
-      <c r="L43" s="18">
+      <c r="M43" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B43)</f>
         <v/>
       </c>
@@ -9689,39 +10509,43 @@
           <t>呪術廻戦展 懐玉玉折 渋谷事変　脱兎クリップのみ(1SET 5個)</t>
         </is>
       </c>
-      <c r="D44" s="16">
+      <c r="D44" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B44)</f>
         <v/>
       </c>
       <c r="E44" s="10">
+        <f>IF(D44&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F44" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B44,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F44" s="11">
+      <c r="G44" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B44,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G44" s="10">
+      <c r="H44" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B44,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H44" s="11">
+      <c r="I44" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B44,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I44" s="10">
+      <c r="J44" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B44,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J44" s="11">
+      <c r="K44" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B44,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K44" s="17">
+      <c r="L44" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B44)</f>
         <v/>
       </c>
-      <c r="L44" s="18">
+      <c r="M44" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B44)</f>
         <v/>
       </c>
@@ -9742,94 +10566,356 @@
           <t>呪術廻戦展 懐玉玉折 渋谷事変 経費（課税10％）</t>
         </is>
       </c>
-      <c r="D45" s="16">
+      <c r="D45" s="10">
         <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B45)</f>
         <v/>
       </c>
       <c r="E45" s="10">
+        <f>IF(D45&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F45" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B45,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="F45" s="11">
+      <c r="G45" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B45,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
         <v/>
       </c>
-      <c r="G45" s="10">
+      <c r="H45" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B45,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="H45" s="11">
+      <c r="I45" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B45,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
         <v/>
       </c>
-      <c r="I45" s="10">
+      <c r="J45" s="11">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B45,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="J45" s="11">
+      <c r="K45" s="12">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B45,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
         <v/>
       </c>
-      <c r="K45" s="17">
+      <c r="L45" s="25">
         <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B45)</f>
         <v/>
       </c>
-      <c r="L45" s="18">
+      <c r="M45" s="26">
         <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B45)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="12" t="n"/>
-      <c r="B46" s="12" t="n"/>
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>QCX2509JKS2FN-8</t>
+        </is>
+      </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
+          <t>呪術廻戦展 懐玉玉折 渋谷事変 経費（課税8％）</t>
+        </is>
+      </c>
+      <c r="D46" s="14">
+        <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B46)</f>
+        <v/>
+      </c>
+      <c r="E46" s="14">
+        <f>IF(D46&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F46" s="15">
+        <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B46,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
+        <v/>
+      </c>
+      <c r="G46" s="16">
+        <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B46,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
+        <v/>
+      </c>
+      <c r="H46" s="15">
+        <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B46,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
+        <v/>
+      </c>
+      <c r="I46" s="16">
+        <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B46,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
+        <v/>
+      </c>
+      <c r="J46" s="15">
+        <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B46,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
+        <v/>
+      </c>
+      <c r="K46" s="16">
+        <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B46,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
+        <v/>
+      </c>
+      <c r="L46" s="27">
+        <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B46)</f>
+        <v/>
+      </c>
+      <c r="M46" s="28">
+        <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>QCX2509JKS2FN-NT</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>呪術廻戦展 懐玉玉折 渋谷事変 経費（非課税）</t>
+        </is>
+      </c>
+      <c r="D47" s="14">
+        <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B47)</f>
+        <v/>
+      </c>
+      <c r="E47" s="14">
+        <f>IF(D47&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F47" s="15">
+        <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B47,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
+        <v/>
+      </c>
+      <c r="G47" s="16">
+        <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B47,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
+        <v/>
+      </c>
+      <c r="H47" s="15">
+        <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B47,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
+        <v/>
+      </c>
+      <c r="I47" s="16">
+        <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B47,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
+        <v/>
+      </c>
+      <c r="J47" s="15">
+        <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B47,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
+        <v/>
+      </c>
+      <c r="K47" s="16">
+        <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B47,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
+        <v/>
+      </c>
+      <c r="L47" s="27">
+        <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B47)</f>
+        <v/>
+      </c>
+      <c r="M47" s="28">
+        <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>QCX2509JKS2FN-RY</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>呪術廻戦展 懐玉玉折 渋谷事変 経費（RY）</t>
+        </is>
+      </c>
+      <c r="D48" s="14">
+        <f>COUNTIFS('XTab DS_1'!$B$2:$B$95,$B48)</f>
+        <v/>
+      </c>
+      <c r="E48" s="14">
+        <f>IF(D48&gt;=2,"重複","単独")</f>
+        <v/>
+      </c>
+      <c r="F48" s="15">
+        <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B48,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
+        <v/>
+      </c>
+      <c r="G48" s="16">
+        <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B48,'XTab DS_1'!$D$2:$D$95,"CX01")</f>
+        <v/>
+      </c>
+      <c r="H48" s="15">
+        <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B48,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
+        <v/>
+      </c>
+      <c r="I48" s="16">
+        <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B48,'XTab DS_1'!$D$2:$D$95,"DB00")</f>
+        <v/>
+      </c>
+      <c r="J48" s="15">
+        <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B48,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
+        <v/>
+      </c>
+      <c r="K48" s="16">
+        <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B48,'XTab DS_1'!$D$2:$D$95,"ZZ01")</f>
+        <v/>
+      </c>
+      <c r="L48" s="27">
+        <f>SUMIFS('XTab DS_1'!$F$2:$F$95,'XTab DS_1'!$B$2:$B$95,$B48)</f>
+        <v/>
+      </c>
+      <c r="M48" s="28">
+        <f>SUMIFS('XTab DS_1'!$G$2:$G$95,'XTab DS_1'!$B$2:$B$95,$B48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="17" t="n"/>
+      <c r="B49" s="17" t="n"/>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="D46" s="12" t="n"/>
-      <c r="E46" s="14">
-        <f>SUM(E2:E45)</f>
-        <v/>
-      </c>
-      <c r="F46" s="15">
-        <f>SUM(F2:F45)</f>
-        <v/>
-      </c>
-      <c r="G46" s="14">
-        <f>SUM(G2:G45)</f>
-        <v/>
-      </c>
-      <c r="H46" s="15">
-        <f>SUM(H2:H45)</f>
-        <v/>
-      </c>
-      <c r="I46" s="14">
-        <f>SUM(I2:I45)</f>
-        <v/>
-      </c>
-      <c r="J46" s="15">
-        <f>SUM(J2:J45)</f>
-        <v/>
-      </c>
-      <c r="K46" s="14">
-        <f>SUM(K2:K45)</f>
-        <v/>
-      </c>
-      <c r="L46" s="15">
-        <f>SUM(L2:L45)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="19" t="inlineStr">
-        <is>
-          <t>※元データ「XTab DS_1」から、2つ以上の倉庫(保管場所)に登録されている品目コードを抽出。数量・金額はSUMIFSで元データから集計（元データ変更で自動再計算）。</t>
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n"/>
+      <c r="F49" s="19">
+        <f>SUM(F2:F48)</f>
+        <v/>
+      </c>
+      <c r="G49" s="20">
+        <f>SUM(G2:G48)</f>
+        <v/>
+      </c>
+      <c r="H49" s="19">
+        <f>SUM(H2:H48)</f>
+        <v/>
+      </c>
+      <c r="I49" s="20">
+        <f>SUM(I2:I48)</f>
+        <v/>
+      </c>
+      <c r="J49" s="19">
+        <f>SUM(J2:J48)</f>
+        <v/>
+      </c>
+      <c r="K49" s="20">
+        <f>SUM(K2:K48)</f>
+        <v/>
+      </c>
+      <c r="L49" s="19">
+        <f>SUM(L2:L48)</f>
+        <v/>
+      </c>
+      <c r="M49" s="20">
+        <f>SUM(M2:M48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="21" t="n"/>
+      <c r="B50" s="21" t="n"/>
+      <c r="C50" s="22" t="inlineStr">
+        <is>
+          <t>うち 重複</t>
+        </is>
+      </c>
+      <c r="D50" s="21" t="n"/>
+      <c r="E50" s="21" t="n"/>
+      <c r="F50" s="23">
+        <f>SUMIFS(F2:F48,E2:E48,"重複")</f>
+        <v/>
+      </c>
+      <c r="G50" s="24">
+        <f>SUMIFS(G2:G48,E2:E48,"重複")</f>
+        <v/>
+      </c>
+      <c r="H50" s="23">
+        <f>SUMIFS(H2:H48,E2:E48,"重複")</f>
+        <v/>
+      </c>
+      <c r="I50" s="24">
+        <f>SUMIFS(I2:I48,E2:E48,"重複")</f>
+        <v/>
+      </c>
+      <c r="J50" s="23">
+        <f>SUMIFS(J2:J48,E2:E48,"重複")</f>
+        <v/>
+      </c>
+      <c r="K50" s="24">
+        <f>SUMIFS(K2:K48,E2:E48,"重複")</f>
+        <v/>
+      </c>
+      <c r="L50" s="23">
+        <f>SUMIFS(L2:L48,E2:E48,"重複")</f>
+        <v/>
+      </c>
+      <c r="M50" s="24">
+        <f>SUMIFS(M2:M48,E2:E48,"重複")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="21" t="n"/>
+      <c r="B51" s="21" t="n"/>
+      <c r="C51" s="22" t="inlineStr">
+        <is>
+          <t>うち 単独</t>
+        </is>
+      </c>
+      <c r="D51" s="21" t="n"/>
+      <c r="E51" s="21" t="n"/>
+      <c r="F51" s="23">
+        <f>SUMIFS(F2:F48,E2:E48,"単独")</f>
+        <v/>
+      </c>
+      <c r="G51" s="24">
+        <f>SUMIFS(G2:G48,E2:E48,"単独")</f>
+        <v/>
+      </c>
+      <c r="H51" s="23">
+        <f>SUMIFS(H2:H48,E2:E48,"単独")</f>
+        <v/>
+      </c>
+      <c r="I51" s="24">
+        <f>SUMIFS(I2:I48,E2:E48,"単独")</f>
+        <v/>
+      </c>
+      <c r="J51" s="23">
+        <f>SUMIFS(J2:J48,E2:E48,"単独")</f>
+        <v/>
+      </c>
+      <c r="K51" s="24">
+        <f>SUMIFS(K2:K48,E2:E48,"単独")</f>
+        <v/>
+      </c>
+      <c r="L51" s="23">
+        <f>SUMIFS(L2:L48,E2:E48,"単独")</f>
+        <v/>
+      </c>
+      <c r="M51" s="24">
+        <f>SUMIFS(M2:M48,E2:E48,"単独")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="29" t="inlineStr">
+        <is>
+          <t>※元データ「XTab DS_1」の全品目を掲載。2つ以上の倉庫(保管場所)に登録されている品目を「重複」（黄色）、1倉庫のみを「単独」と表示。数量・金額はSUMIFSで元データから集計（元データ変更で自動再計算）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:M48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>